--- a/Lab Work/Lab 8 Amit Bikram Mishra.xlsx
+++ b/Lab Work/Lab 8 Amit Bikram Mishra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMIT\Desktop\ANUDIP\AmitAnudipAF057117047\Lab Work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B4F6F6-0CE7-4E3C-9847-32CA5C9E994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1677251-381E-4A36-9BB4-815EAA5243D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,6 +375,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -384,62 +393,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -934,31 +934,31 @@
     </row>
     <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="5"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="13"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="16">
         <f>INDEX(D2:H7, MATCH("PRODC", B2:B7, 0), MATCH("Mar Sales", D1:H1, 0))</f>
         <v>220</v>
@@ -967,207 +967,207 @@
       <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
       <c r="G12" s="14"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="21"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
       <c r="G13" s="14"/>
-      <c r="H13" s="19" t="str">
+      <c r="H13" s="3" t="str">
         <f>INDEX(C1:H7,MATCH(B6,B1:B7,0),MATCH(C1,C1:H1,0))</f>
         <v>Furniture</v>
       </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="21"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
       <c r="G14" s="14"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="21"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
       <c r="G15" s="14"/>
-      <c r="H15" s="19">
+      <c r="H15" s="3">
         <f>MAX(INDEX(D2:H7, MATCH("PRODB", B2:B7, 0), 0))</f>
         <v>190</v>
       </c>
-      <c r="I15" s="20"/>
-      <c r="J15" s="21"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
       <c r="G16" s="14"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
       <c r="G17" s="14"/>
-      <c r="H17" s="19" t="str">
+      <c r="H17" s="3" t="str">
         <f>INDEX(D1:H1, MATCH(MAX(INDEX(D2:H7, MATCH("PRODA", B2:B7, 0), 0)), INDEX(D2:H7, MATCH("PRODA", B2:B7, 0), 0), 0))</f>
         <v>May Sales</v>
       </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" s="9"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
       <c r="G18" s="14"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
       <c r="G19" s="14"/>
-      <c r="H19" s="19">
+      <c r="H19" s="3">
         <f>SUMIF(C2:C7,"Electronics", INDEX(D2:H7,0,MATCH("Apr Sales",D1:H1,0)))</f>
         <v>540</v>
       </c>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
       <c r="G20" s="14"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="21"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
       <c r="G21" s="14"/>
-      <c r="H21" s="19">
+      <c r="H21" s="3">
         <f>AVERAGE(INDEX(D2:H7, MATCH("PRODD", B2:B7, 0), 0))</f>
         <v>110</v>
       </c>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="9"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
       <c r="G22" s="14"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
       <c r="G23" s="14"/>
-      <c r="H23" s="19">
+      <c r="H23" s="3">
         <f>INDEX(D2:H7,MATCH(105,A2:A7,0),MATCH("May Sales",D1:H1,0))</f>
         <v>260</v>
       </c>
-      <c r="I23" s="20"/>
-      <c r="J23" s="21"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" s="9"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="21"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
       <c r="G25" s="14"/>
-      <c r="H25" s="19">
+      <c r="H25" s="3">
         <f>INDEX(D2:H7, MATCH(L25, B2:B7, 0), MATCH(M25, D1:H1, 0))</f>
         <v>140</v>
       </c>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
       <c r="L25" s="2" t="s">
         <v>8</v>
       </c>
@@ -1176,16 +1176,16 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="29.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="24"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -1194,11 +1194,6 @@
     <mergeCell ref="A21:G22"/>
     <mergeCell ref="A23:G24"/>
     <mergeCell ref="A25:G26"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H11:J12"/>
-    <mergeCell ref="H13:J14"/>
-    <mergeCell ref="H15:J16"/>
-    <mergeCell ref="H17:J18"/>
     <mergeCell ref="H19:J20"/>
     <mergeCell ref="H21:J22"/>
     <mergeCell ref="A10:G10"/>
@@ -1207,6 +1202,11 @@
     <mergeCell ref="A15:G16"/>
     <mergeCell ref="A17:G18"/>
     <mergeCell ref="A19:G20"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H11:J12"/>
+    <mergeCell ref="H13:J14"/>
+    <mergeCell ref="H15:J16"/>
+    <mergeCell ref="H17:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
